--- a/docs/templates/A0-SHORE.xlsx
+++ b/docs/templates/A0-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6158942-5E44-4685-80D8-F263545C1403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC4D3F50-4B27-4797-AEDA-C1ACD9E3DFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BB3708A4-C3DC-4662-98F9-C9842099189E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{062A3022-988B-4D3E-97A3-B68251A8E3FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>OUT</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t xml:space="preserve">เที่ยวเรือ </t>
+  </si>
+  <si>
+    <t>***** อนุญาตให้ลูกค้ากรอกรายละเอียดในฟอร์ม ช. เองได้ หากผิดผลาดใดๆลูกค้าจะเป็นคนรับผิดชอบทุกประการ *****</t>
   </si>
 </sst>
 </file>
@@ -889,23 +892,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{F1C59FD9-8A87-4125-A6A3-01B525915072}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{CEBB0093-1651-4687-851B-3F58506ECE8F}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{0B26B5B1-6526-44CA-BA2A-E9ADAF1C6462}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{3223AE58-A495-4B90-A274-9F1AC477356A}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
-    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{C190B971-6946-4A46-862B-C0EBC11169BF}"/>
+    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{367D629F-7C2C-44D9-99A4-669A7251F79C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -937,10 +940,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10256" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
+        <xdr:cNvPr id="10260" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9609047-E884-6D00-997D-92DFD79A9B65}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{346D39FA-FF9F-BB85-6A6D-B22960474B35}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1011,10 +1014,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10257" name="Picture 23" descr="Logos">
+        <xdr:cNvPr id="10261" name="Picture 23" descr="Logos">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47D6F6D6-BD0E-97BB-69F7-2EF22C836A5C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0818981B-0DF4-8E53-9B80-4D3DD79F764D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1422,7 +1425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA7241D-3272-427A-BABE-23022BB8B6F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEE9834-6AC4-42CE-91BD-929F5C99693E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1786,7 +1789,9 @@
     <row r="24" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="57"/>
       <c r="B24" s="58"/>
-      <c r="C24" s="103"/>
+      <c r="C24" s="103" t="s">
+        <v>32</v>
+      </c>
       <c r="D24" s="104"/>
       <c r="E24" s="104"/>
       <c r="F24" s="104"/>
@@ -2033,7 +2038,7 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{8A747905-47BD-4D19-ADFE-AAD34B7BB9C8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{77E4C346-BD55-423A-B5E1-EAF04CBAB732}">
       <formula1>$C$29:$C$33</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/templates/A0-SHORE.xlsx
+++ b/docs/templates/A0-SHORE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC4D3F50-4B27-4797-AEDA-C1ACD9E3DFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A443B3C9-AD45-482A-88E6-BF7B4187360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{062A3022-988B-4D3E-97A3-B68251A8E3FA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DDE93CD-E8AA-4B72-AE6C-0A5C23F6BE5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -905,10 +905,10 @@
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{0B26B5B1-6526-44CA-BA2A-E9ADAF1C6462}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{3223AE58-A495-4B90-A274-9F1AC477356A}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{7217D2F4-2152-4A2C-B71C-3644EF194862}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{06D226A5-BCD0-46E5-8AF6-DDFB05DB92B9}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
-    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{367D629F-7C2C-44D9-99A4-669A7251F79C}"/>
+    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{7A925A92-1EFE-4C7F-B039-C034ED14B30F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -928,22 +928,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
+      <xdr:colOff>45720</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:colOff>640080</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
+      <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10260" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{346D39FA-FF9F-BB85-6A6D-B22960474B35}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1609959-B8AD-C280-65C0-230B36EA8FFB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -966,8 +966,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="53340" y="38100"/>
-          <a:ext cx="1295400" cy="480060"/>
+          <a:off x="45720" y="30480"/>
+          <a:ext cx="1143000" cy="434340"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1002,22 +1002,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>769620</xdr:colOff>
+      <xdr:colOff>617220</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>251460</xdr:rowOff>
+      <xdr:rowOff>198120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10261" name="Picture 23" descr="Logos">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0818981B-0DF4-8E53-9B80-4D3DD79F764D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CFB4B45-EF58-DE56-BC2F-EA0F7D2A3170}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1040,8 +1040,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6019800" y="45720"/>
-          <a:ext cx="1295400" cy="457200"/>
+          <a:off x="5943600" y="38100"/>
+          <a:ext cx="1219200" cy="411480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1425,7 +1425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEE9834-6AC4-42CE-91BD-929F5C99693E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD32BB2-8D72-4FF4-A040-E8A819C791E3}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2038,7 +2038,7 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{77E4C346-BD55-423A-B5E1-EAF04CBAB732}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{53D2FDC3-5F83-46B9-BC6D-C3CB34735F00}">
       <formula1>$C$29:$C$33</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/templates/A0-SHORE.xlsx
+++ b/docs/templates/A0-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A443B3C9-AD45-482A-88E6-BF7B4187360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CF900B4-6A2D-4500-B162-62F0FB96584B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DDE93CD-E8AA-4B72-AE6C-0A5C23F6BE5E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDB8F8DC-9861-4279-8B67-74DC7062DA0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -905,10 +905,10 @@
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{7217D2F4-2152-4A2C-B71C-3644EF194862}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{06D226A5-BCD0-46E5-8AF6-DDFB05DB92B9}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{34C9014E-A582-485B-BED1-60E40AA4B401}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{C1C46449-75B8-442A-A452-25CAD90EF6F8}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
-    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{7A925A92-1EFE-4C7F-B039-C034ED14B30F}"/>
+    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{42BCB61B-8DB7-4663-8E82-95330C73558D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -943,7 +943,7 @@
         <xdr:cNvPr id="10260" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1609959-B8AD-C280-65C0-230B36EA8FFB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9ED5409-48F0-8FD5-1B66-EA31B692F0E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1017,7 +1017,7 @@
         <xdr:cNvPr id="10261" name="Picture 23" descr="Logos">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CFB4B45-EF58-DE56-BC2F-EA0F7D2A3170}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDD2FB27-8F31-2E39-9D2A-BE425B4ECC07}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1425,7 +1425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD32BB2-8D72-4FF4-A040-E8A819C791E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C657B9C-2C41-4D31-B1E8-F38C4B7A77F3}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2038,7 +2038,7 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{53D2FDC3-5F83-46B9-BC6D-C3CB34735F00}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{D1044B28-7317-4E7A-AEBF-1E11DC33A3C1}">
       <formula1>$C$29:$C$33</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/templates/A0-SHORE.xlsx
+++ b/docs/templates/A0-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CF900B4-6A2D-4500-B162-62F0FB96584B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76804D7F-2A58-4764-8198-D32128AD8BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDB8F8DC-9861-4279-8B67-74DC7062DA0A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1AA25253-5B62-4682-8DB2-E6AAEEFA173C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -905,10 +905,10 @@
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{34C9014E-A582-485B-BED1-60E40AA4B401}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{C1C46449-75B8-442A-A452-25CAD90EF6F8}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{15E33FBE-EDDE-4D4F-96A7-186CBC09B611}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{BBAE3825-3F11-4D9D-9252-2D589759CA4B}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
-    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{42BCB61B-8DB7-4663-8E82-95330C73558D}"/>
+    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{311BE044-9326-4299-996D-311BFCB4F5F6}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -943,7 +943,7 @@
         <xdr:cNvPr id="10260" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9ED5409-48F0-8FD5-1B66-EA31B692F0E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58F475AC-1B47-7967-226B-2BC9503E2DB7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1017,7 +1017,7 @@
         <xdr:cNvPr id="10261" name="Picture 23" descr="Logos">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDD2FB27-8F31-2E39-9D2A-BE425B4ECC07}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC8C1A99-0B91-59EC-C1E2-859C3C23C31C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1425,7 +1425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C657B9C-2C41-4D31-B1E8-F38C4B7A77F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A0F46B-18DD-4467-8D01-B0239ECBF0EE}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2038,7 +2038,7 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{D1044B28-7317-4E7A-AEBF-1E11DC33A3C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{B1C6E0D3-7F5C-4D81-AD15-B66CBAD3C042}">
       <formula1>$C$29:$C$33</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/templates/A0-SHORE.xlsx
+++ b/docs/templates/A0-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76804D7F-2A58-4764-8198-D32128AD8BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5FEF618-ABB3-424E-A0C0-A846025AC62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1AA25253-5B62-4682-8DB2-E6AAEEFA173C}"/>
+    <workbookView xWindow="30240" yWindow="1440" windowWidth="21600" windowHeight="11235" xr2:uid="{25497A20-2393-424A-BB61-DA28423875DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>OUT</t>
   </si>
@@ -95,9 +95,6 @@
     <t xml:space="preserve">(  ) 20' จำนวน </t>
   </si>
   <si>
-    <t>\</t>
-  </si>
-  <si>
     <t>VENT</t>
   </si>
   <si>
@@ -110,21 +107,12 @@
     <t xml:space="preserve">หมายเหตุ 1 .หากไม่มีลายมือชื่อจริงและเบอร์โทรเจ้าของสินค้า/ผู้ส่งออก </t>
   </si>
   <si>
-    <t xml:space="preserve">เวลา                                        </t>
-  </si>
-  <si>
     <t>นำไปยัง Customer …….........   ( XXX   )  ตู้สินค้าเปล่า   ( )  ตู้บรรจุสินค้า</t>
   </si>
   <si>
     <t>วันที่ .................................................  บริษัท .....HEUNG A LINE CO.,LTD. C/O HEUNG A  LINE (THAILAND)CO.,LTD.  (      ) รถยนต์   (      ) รถไฟ</t>
   </si>
   <si>
-    <t>ชื่อ-เบอร์โทร........HEUNG-A ...............................</t>
-  </si>
-  <si>
-    <t>CREDIT HEUNG-A</t>
-  </si>
-  <si>
     <t>โดยเรือ……...............…….....….    เที่ยวเรือ .......….....…..... เที่ยววันที่ ……..............</t>
   </si>
   <si>
@@ -135,18 +123,20 @@
   </si>
   <si>
     <t>***** อนุญาตให้ลูกค้ากรอกรายละเอียดในฟอร์ม ช. เองได้ หากผิดผลาดใดๆลูกค้าจะเป็นคนรับผิดชอบทุกประการ *****</t>
+  </si>
+  <si>
+    <t>CASH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="194" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="217" formatCode="[$-1010000]d/m/yyyy\ h:mm\ &quot;น.&quot;;@"/>
     <numFmt numFmtId="218" formatCode="#,##0.################"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -237,6 +227,12 @@
       <family val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
@@ -250,9 +246,43 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Angsana New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Angsana New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Bookman Old Style"/>
       <family val="1"/>
     </font>
     <font>
@@ -261,72 +291,6 @@
       <color rgb="FF0033CC"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -344,13 +308,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -361,18 +331,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -480,21 +444,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -520,6 +469,21 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -538,43 +502,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -607,24 +534,149 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="194" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -656,12 +708,7 @@
     <xf numFmtId="194" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="194" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -676,14 +723,8 @@
     <xf numFmtId="194" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="3" borderId="10" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -692,112 +733,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="218" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="218" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="4" borderId="12" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="194" fontId="23" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="194" fontId="23" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="218" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="4" borderId="12" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="23" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="194" fontId="23" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="194" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="194" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="194" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="218" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="3" borderId="10" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="194" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="194" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="194" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="194" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="25" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="218" fontId="25" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="25" fillId="3" borderId="10" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="25" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="218" fontId="20" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="4" borderId="24" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="24" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -808,16 +852,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -835,80 +879,80 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="194" fontId="28" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="194" fontId="28" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="194" fontId="28" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="217" fontId="29" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="217" fontId="29" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="217" fontId="29" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="23" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="23" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="23" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="23" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="23" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="23" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{15E33FBE-EDDE-4D4F-96A7-186CBC09B611}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{BBAE3825-3F11-4D9D-9252-2D589759CA4B}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{D9803F3B-99F6-41FC-A38C-0E7193C99F4D}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{76CDE59E-B52D-462B-A3AD-8B05D71ED5B6}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
-    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{311BE044-9326-4299-996D-311BFCB4F5F6}"/>
+    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{9BF20E84-90B3-4490-B693-18BE885F184F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -940,10 +984,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10260" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
+        <xdr:cNvPr id="10264" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58F475AC-1B47-7967-226B-2BC9503E2DB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{275CB9FF-CDFF-0171-8CBB-5145F122A9A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1014,10 +1058,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10261" name="Picture 23" descr="Logos">
+        <xdr:cNvPr id="10265" name="Picture 23" descr="Logos">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC8C1A99-0B91-59EC-C1E2-859C3C23C31C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D36A2CE-0F43-7E0B-AE49-75273416EFCC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1425,7 +1469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A0F46B-18DD-4467-8D01-B0239ECBF0EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A3C8F0-4E55-4FF4-91BE-712ED170159E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1447,90 +1491,90 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
     </row>
     <row r="3" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="89"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="92"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="84"/>
     </row>
     <row r="5" spans="1:11" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="19"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="16"/>
     </row>
     <row r="6" spans="1:11" ht="20.399999999999999" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="76"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
       <c r="H6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="20"/>
+        <v>27</v>
+      </c>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A7" s="78"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="22" t="s">
-        <v>25</v>
+      <c r="A7" s="70"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1541,19 +1585,19 @@
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="81"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="83"/>
+      <c r="A8" s="73"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="75"/>
       <c r="D8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="38"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="30"/>
+      <c r="I8" s="28"/>
       <c r="J8" s="9" t="s">
         <v>16</v>
       </c>
@@ -1562,22 +1606,22 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="85"/>
-      <c r="C9" s="86"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="78"/>
       <c r="D9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="25"/>
+        <v>25</v>
+      </c>
+      <c r="K9" s="20"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A10" s="84"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="22" t="s">
-        <v>22</v>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -1588,19 +1632,19 @@
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A11" s="84"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="86"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="78"/>
       <c r="D11" s="8" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="40"/>
-      <c r="I11" s="41"/>
+        <v>20</v>
+      </c>
+      <c r="H11" s="30"/>
+      <c r="I11" s="31"/>
       <c r="J11" s="9" t="s">
         <v>16</v>
       </c>
@@ -1609,416 +1653,422 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="29"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="24"/>
     </row>
     <row r="13" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="93"/>
-      <c r="C13" s="30" t="s">
+      <c r="B13" s="85"/>
+      <c r="C13" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="30" t="s">
+      <c r="F13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="31" t="s">
+      <c r="I13" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="30" t="s">
+      <c r="K13" s="25" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="66"/>
+      <c r="A14" s="64"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="47"/>
     </row>
     <row r="15" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="72"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="66"/>
+      <c r="A15" s="64"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="47"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="72"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="46"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="32"/>
     </row>
     <row r="17" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="72"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="46"/>
+      <c r="A17" s="64"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="32"/>
     </row>
     <row r="18" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="72"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="46"/>
+      <c r="A18" s="64"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="32"/>
     </row>
     <row r="19" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="72"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="46"/>
+      <c r="A19" s="64"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="32"/>
     </row>
     <row r="20" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="72"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="46"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="32"/>
     </row>
     <row r="21" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="72"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="46"/>
+      <c r="A21" s="64"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="72"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="46"/>
+      <c r="A22" s="64"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="32"/>
     </row>
     <row r="23" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="72"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="46"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="32"/>
     </row>
     <row r="24" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="57"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="103" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="46"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="89" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="32"/>
     </row>
     <row r="25" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="101"/>
-      <c r="B25" s="102"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="35"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="33"/>
-    </row>
-    <row r="26" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="45"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="43"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="61"/>
-    </row>
-    <row r="27" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="98" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="99"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="95"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="57"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="27"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A26" s="92"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="94"/>
+      <c r="K26" s="54"/>
+    </row>
+    <row r="27" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="95"/>
+      <c r="B27" s="96"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="96"/>
       <c r="H27" s="96"/>
       <c r="I27" s="96"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="97"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="21.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D28" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="A28" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
       <c r="K28" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C29" s="15"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C30" s="15"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="62"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C31" s="15"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C32" s="15"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="C33" s="15"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D34" s="64"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="62"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D35" s="64"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D36" s="64"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D37" s="63"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="62"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="62"/>
-      <c r="J37" s="62"/>
-      <c r="K37" s="62"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D38" s="63"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D39" s="63"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="62"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
     </row>
     <row r="40" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D40" s="64"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="62"/>
-      <c r="H40" s="62"/>
-      <c r="I40" s="62"/>
-      <c r="J40" s="62"/>
-      <c r="K40" s="62"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
     </row>
     <row r="41" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D41" s="64"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="62"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
     </row>
     <row r="42" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D42" s="64"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62"/>
-      <c r="K42" s="62"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D43" s="64"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="62"/>
-      <c r="H43" s="62"/>
-      <c r="I43" s="62"/>
-      <c r="J43" s="62"/>
-      <c r="K43" s="62"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="G27:K27"/>
-    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A26:J27"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A6:C8"/>
     <mergeCell ref="A9:C11"/>
@@ -2026,22 +2076,14 @@
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E6:G6"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A28:J28"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{B1C6E0D3-7F5C-4D81-AD15-B66CBAD3C042}">
-      <formula1>$C$29:$C$33</formula1>
-    </dataValidation>
-  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.16" right="0.15748031496063" top="0.16" bottom="0" header="0.16" footer="0.16"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>

--- a/docs/templates/A0-SHORE.xlsx
+++ b/docs/templates/A0-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5FEF618-ABB3-424E-A0C0-A846025AC62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20D6C069-16A7-4EFF-9FE6-1FC86D9FC995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="1440" windowWidth="21600" windowHeight="11235" xr2:uid="{25497A20-2393-424A-BB61-DA28423875DC}"/>
+    <workbookView xWindow="30675" yWindow="1875" windowWidth="21600" windowHeight="11235" xr2:uid="{35DC54C8-1EDD-451D-979A-F3E62EDC7227}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -136,7 +136,7 @@
     <numFmt numFmtId="194" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="218" formatCode="#,##0.################"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -230,6 +230,11 @@
       <b/>
       <sz val="14"/>
       <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Angsana New"/>
       <family val="1"/>
     </font>
     <font>
@@ -510,101 +515,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -628,6 +538,101 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -671,7 +676,7 @@
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="194" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
@@ -708,7 +713,7 @@
     <xf numFmtId="194" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="194" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -739,10 +744,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -773,81 +778,114 @@
     <xf numFmtId="9" fontId="15" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="194" fontId="24" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="194" fontId="24" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="22" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="218" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="4" borderId="12" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="218" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="4" borderId="15" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="17" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="194" fontId="17" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="194" fontId="23" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="194" fontId="23" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="218" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="4" borderId="12" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="23" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="194" fontId="23" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="218" fontId="20" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="25" fillId="4" borderId="24" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="24" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="17" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="194" fontId="17" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="17" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="17" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="17" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="17" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -909,50 +947,17 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="23" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="23" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="23" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="23" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="23" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="23" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{D9803F3B-99F6-41FC-A38C-0E7193C99F4D}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{76CDE59E-B52D-462B-A3AD-8B05D71ED5B6}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{CCFCC0EA-9C68-4B0F-AA2E-12F07566CE38}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{1C5A8320-EC09-433C-A859-5556C26813F9}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
-    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{9BF20E84-90B3-4490-B693-18BE885F184F}"/>
+    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{42B8C807-99ED-46E0-9CCE-E17054A3FC80}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -984,10 +989,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10264" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
+        <xdr:cNvPr id="10266" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{275CB9FF-CDFF-0171-8CBB-5145F122A9A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72F2CB6D-8231-3EC9-20EF-64869B8DE5C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1058,10 +1063,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10265" name="Picture 23" descr="Logos">
+        <xdr:cNvPr id="10267" name="Picture 23" descr="Logos">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D36A2CE-0F43-7E0B-AE49-75273416EFCC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D410402-E1DE-A0EC-95A6-2F0135CEDE30}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1469,7 +1474,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A3C8F0-4E55-4FF4-91BE-712ED170159E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94E47F4-1EB2-48F9-B1FF-EEF31FAE21F9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1491,49 +1496,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="3" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="81"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="92"/>
     </row>
     <row r="4" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="84"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="95"/>
     </row>
     <row r="5" spans="1:11" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A5" s="3" t="s">
@@ -1551,28 +1556,28 @@
       <c r="K5" s="16"/>
     </row>
     <row r="6" spans="1:11" ht="20.399999999999999" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="69"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="80"/>
       <c r="D6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
       <c r="H6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
       <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A7" s="70"/>
-      <c r="B7" s="71"/>
-      <c r="C7" s="72"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="83"/>
       <c r="D7" s="19" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1590,9 @@
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="73"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="75"/>
+      <c r="A8" s="84"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="86"/>
       <c r="D8" s="8" t="s">
         <v>18</v>
       </c>
@@ -1606,20 +1611,20 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="78"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
       <c r="D9" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K9" s="20"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A10" s="76"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="78"/>
+      <c r="A10" s="87"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="89"/>
       <c r="D10" s="19" t="s">
         <v>21</v>
       </c>
@@ -1632,9 +1637,9 @@
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A11" s="76"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="78"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="8" t="s">
         <v>18</v>
       </c>
@@ -1668,10 +1673,10 @@
       <c r="K12" s="24"/>
     </row>
     <row r="13" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="85"/>
+      <c r="B13" s="96"/>
       <c r="C13" s="25" t="s">
         <v>4</v>
       </c>
@@ -1701,8 +1706,8 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="64"/>
-      <c r="B14" s="65"/>
+      <c r="A14" s="66"/>
+      <c r="B14" s="67"/>
       <c r="C14" s="46"/>
       <c r="D14" s="47"/>
       <c r="E14" s="48"/>
@@ -1714,8 +1719,8 @@
       <c r="K14" s="47"/>
     </row>
     <row r="15" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="64"/>
-      <c r="B15" s="65"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="67"/>
       <c r="C15" s="46"/>
       <c r="D15" s="47"/>
       <c r="E15" s="48"/>
@@ -1727,8 +1732,8 @@
       <c r="K15" s="47"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="64"/>
-      <c r="B16" s="65"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="67"/>
       <c r="C16" s="40"/>
       <c r="D16" s="32"/>
       <c r="E16" s="33"/>
@@ -1740,8 +1745,8 @@
       <c r="K16" s="32"/>
     </row>
     <row r="17" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="64"/>
-      <c r="B17" s="65"/>
+      <c r="A17" s="66"/>
+      <c r="B17" s="67"/>
       <c r="C17" s="40"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33"/>
@@ -1753,8 +1758,8 @@
       <c r="K17" s="32"/>
     </row>
     <row r="18" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="64"/>
-      <c r="B18" s="65"/>
+      <c r="A18" s="66"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="40"/>
       <c r="D18" s="32"/>
       <c r="E18" s="33"/>
@@ -1766,8 +1771,8 @@
       <c r="K18" s="32"/>
     </row>
     <row r="19" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="64"/>
-      <c r="B19" s="65"/>
+      <c r="A19" s="66"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="40"/>
       <c r="D19" s="32"/>
       <c r="E19" s="33"/>
@@ -1779,8 +1784,8 @@
       <c r="K19" s="32"/>
     </row>
     <row r="20" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="64"/>
-      <c r="B20" s="65"/>
+      <c r="A20" s="66"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="40"/>
       <c r="D20" s="32"/>
       <c r="E20" s="33"/>
@@ -1792,8 +1797,8 @@
       <c r="K20" s="32"/>
     </row>
     <row r="21" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="64"/>
-      <c r="B21" s="65"/>
+      <c r="A21" s="66"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="40"/>
       <c r="D21" s="32"/>
       <c r="E21" s="33"/>
@@ -1805,8 +1810,8 @@
       <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="64"/>
-      <c r="B22" s="65"/>
+      <c r="A22" s="66"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="40"/>
       <c r="D22" s="32"/>
       <c r="E22" s="33"/>
@@ -1818,8 +1823,8 @@
       <c r="K22" s="32"/>
     </row>
     <row r="23" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="64"/>
-      <c r="B23" s="65"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="67"/>
       <c r="C23" s="39"/>
       <c r="D23" s="32"/>
       <c r="E23" s="33"/>
@@ -1833,72 +1838,72 @@
     <row r="24" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="41"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="91"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="70"/>
       <c r="K24" s="32"/>
     </row>
     <row r="25" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="56" t="s">
+      <c r="A25" s="64"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="57"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="62"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="60"/>
       <c r="K25" s="27"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A26" s="92"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="94"/>
-      <c r="K26" s="54"/>
-    </row>
-    <row r="27" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="95"/>
-      <c r="B27" s="96"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="96"/>
-      <c r="E27" s="96"/>
-      <c r="F27" s="96"/>
-      <c r="G27" s="96"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="53"/>
+    <row r="26" spans="1:11" ht="25.8" x14ac:dyDescent="0.65">
+      <c r="A26" s="71"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="61"/>
+    </row>
+    <row r="27" spans="1:11" ht="26.4" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="A27" s="74"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="76"/>
+      <c r="K27" s="62"/>
     </row>
     <row r="28" spans="1:11" ht="21.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="63" t="s">
+      <c r="A28" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="97"/>
       <c r="K28" s="7" t="s">
         <v>15</v>
       </c>
@@ -2060,6 +2065,19 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A6:C8"/>
+    <mergeCell ref="A9:C11"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E6:G6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A23:B23"/>
@@ -2069,19 +2087,6 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A6:C8"/>
-    <mergeCell ref="A9:C11"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/docs/templates/A0-SHORE.xlsx
+++ b/docs/templates/A0-SHORE.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20D6C069-16A7-4EFF-9FE6-1FC86D9FC995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9072C8D0-2260-4CBE-B93C-3A3BCF6C5424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30675" yWindow="1875" windowWidth="21600" windowHeight="11235" xr2:uid="{35DC54C8-1EDD-451D-979A-F3E62EDC7227}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CF2CF30-9561-47AD-9AE4-D232BAF72AF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>OUT</t>
   </si>
@@ -83,9 +83,6 @@
     <t>VGM</t>
   </si>
   <si>
-    <t>COM 13 Rev. C</t>
-  </si>
-  <si>
     <t xml:space="preserve"> ตู้ </t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t>นำไปยัง Customer …….........   (    )  ตู้สินค้าเปล่า   ( XX )  ตู้บรรจุสินค้า</t>
   </si>
   <si>
-    <t xml:space="preserve">หมายเหตุ 1 .หากไม่มีลายมือชื่อจริงและเบอร์โทรเจ้าของสินค้า/ผู้ส่งออก </t>
-  </si>
-  <si>
     <t>นำไปยัง Customer …….........   ( XXX   )  ตู้สินค้าเปล่า   ( )  ตู้บรรจุสินค้า</t>
   </si>
   <si>
@@ -126,6 +120,18 @@
   </si>
   <si>
     <t>CASH</t>
+  </si>
+  <si>
+    <t>NAME / ชื่อ :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL / โทร :   </t>
+  </si>
+  <si>
+    <t>EMAIL :</t>
+  </si>
+  <si>
+    <t>Date / Time :</t>
   </si>
 </sst>
 </file>
@@ -174,11 +180,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="15"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -209,12 +210,6 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="8.25"/>
       <color indexed="8"/>
       <name val="Tahoma"/>
@@ -233,9 +228,21 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="18"/>
-      <name val="Angsana New"/>
+      <sz val="14"/>
+      <name val="Cordia New"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="AngsanaUPC"/>
       <family val="1"/>
+      <charset val="222"/>
     </font>
     <font>
       <sz val="11"/>
@@ -271,13 +278,6 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="0"/>
       <name val="Angsana New"/>
@@ -296,6 +296,13 @@
       <color rgb="FF0033CC"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -341,7 +348,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -512,16 +519,76 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
+      <left/>
+      <right/>
+      <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -534,154 +601,22 @@
       <top style="thin">
         <color indexed="63"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="194" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -695,16 +630,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="194" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -741,7 +673,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -750,57 +682,48 @@
     <xf numFmtId="49" fontId="21" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="218" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="4" borderId="12" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="218" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="4" borderId="12" xfId="5" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="194" fontId="24" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="194" fontId="23" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="194" fontId="24" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="22" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
+    <xf numFmtId="194" fontId="23" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="22" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -813,117 +736,111 @@
     <xf numFmtId="49" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="4" borderId="12" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="22" fillId="4" borderId="12" xfId="5" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="22" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="14" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="218" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="4" borderId="15" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="25" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="17" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="194" fontId="17" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="218" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="4" borderId="12" xfId="5" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="24" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="17" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="17" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="17" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="17" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="17" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="17" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -935,29 +852,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{CCFCC0EA-9C68-4B0F-AA2E-12F07566CE38}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{1C5A8320-EC09-433C-A859-5556C26813F9}"/>
-    <cellStyle name="Percent" xfId="4" builtinId="5"/>
-    <cellStyle name="ปกติ 10" xfId="5" xr:uid="{42B8C807-99ED-46E0-9CCE-E17054A3FC80}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{B2D45115-5A21-4C07-A199-BDC0ADEB367C}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{E07599C1-EE65-4008-A0E6-A70FF8503192}"/>
+    <cellStyle name="Normal_CHORE" xfId="4" xr:uid="{86101A8C-CAEE-47EC-B21F-4AB23C311EE4}"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="ปกติ 10" xfId="6" xr:uid="{4503FE9E-942A-402A-B1F9-059A2AA8D545}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -982,17 +909,17 @@
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>640080</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10266" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
+        <xdr:cNvPr id="10268" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72F2CB6D-8231-3EC9-20EF-64869B8DE5C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7647A17-E2FE-C195-FA21-9FC77ACEB77C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1016,7 +943,7 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="45720" y="30480"/>
-          <a:ext cx="1143000" cy="434340"/>
+          <a:ext cx="1463040" cy="434340"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1050,23 +977,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>617220</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>198120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10267" name="Picture 23" descr="Logos">
+        <xdr:cNvPr id="10269" name="Picture 23" descr="Logos">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D410402-E1DE-A0EC-95A6-2F0135CEDE30}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF952D7E-8DCB-2514-5E12-E2F713D99735}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1089,7 +1016,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5943600" y="38100"/>
+          <a:off x="6263640" y="38100"/>
           <a:ext cx="1219200" cy="411480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1474,619 +1401,755 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94E47F4-1EB2-48F9-B1FF-EEF31FAE21F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA3B5D7D-F151-410D-8E56-3925B9E5AB6C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K43"/>
+  <dimension ref="A2:L49"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="19.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="2.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.5546875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="3" width="4.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="53.5546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="77" t="s">
+    <row r="2" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-    </row>
-    <row r="3" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="90" t="s">
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+    </row>
+    <row r="3" spans="1:12" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A3" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="92"/>
-    </row>
-    <row r="4" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="93" t="s">
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="88"/>
+    </row>
+    <row r="4" spans="1:12" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A4" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="95"/>
-    </row>
-    <row r="5" spans="1:11" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="91"/>
+    </row>
+    <row r="5" spans="1:12" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" spans="1:12" ht="20.399999999999999" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="16"/>
-    </row>
-    <row r="6" spans="1:11" ht="20.399999999999999" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="17"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A7" s="81"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="6"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="16"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A7" s="77"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="18" t="s">
+        <v>21</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="84"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29" t="s">
+      <c r="K7" s="6"/>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="27"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="29"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A9" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="19"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A10" s="83"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="30"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A9" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A10" s="87"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="8" t="s">
+      <c r="K10" s="6"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A11" s="83"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="92" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="92"/>
+      <c r="C13" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="30"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="24"/>
-    </row>
-    <row r="13" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="26" t="s">
+      <c r="K13" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="25" t="s">
+      <c r="L13" s="24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="66"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="47"/>
-    </row>
-    <row r="15" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="66"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="47"/>
-    </row>
-    <row r="16" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="66"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="32"/>
-    </row>
-    <row r="17" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="66"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="32"/>
-    </row>
-    <row r="18" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="66"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="32"/>
-    </row>
-    <row r="19" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="66"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="32"/>
-    </row>
-    <row r="20" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="66"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="32"/>
-    </row>
-    <row r="21" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="66"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="32"/>
-    </row>
-    <row r="22" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="66"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="32"/>
-    </row>
-    <row r="23" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="66"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="32"/>
-    </row>
-    <row r="24" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="41"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="70"/>
-      <c r="K24" s="32"/>
-    </row>
-    <row r="25" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="64"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="55"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="60"/>
-      <c r="K25" s="27"/>
-    </row>
-    <row r="26" spans="1:11" ht="25.8" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="71"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="43"/>
+    </row>
+    <row r="15" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="43"/>
+    </row>
+    <row r="16" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="43"/>
+    </row>
+    <row r="17" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="38"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="43"/>
+    </row>
+    <row r="18" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="38"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="43"/>
+    </row>
+    <row r="19" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="38"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="43"/>
+    </row>
+    <row r="20" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="43"/>
+    </row>
+    <row r="21" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="43"/>
+    </row>
+    <row r="22" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="43"/>
+    </row>
+    <row r="23" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="43"/>
+    </row>
+    <row r="24" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="71"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="43"/>
+    </row>
+    <row r="25" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="71"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="31"/>
+    </row>
+    <row r="26" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="71"/>
       <c r="B26" s="72"/>
-      <c r="C26" s="72"/>
+      <c r="C26" s="71"/>
       <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="61"/>
-    </row>
-    <row r="27" spans="1:11" ht="26.4" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A27" s="74"/>
-      <c r="B27" s="75"/>
-      <c r="C27" s="75"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="62"/>
-    </row>
-    <row r="28" spans="1:11" ht="21.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="97" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="97"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="97"/>
-      <c r="H28" s="97"/>
-      <c r="I28" s="97"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C29" s="13"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="43"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C30" s="13"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C31" s="13"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C32" s="13"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-    </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="C33" s="13"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-    </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D34" s="45"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="43"/>
-    </row>
-    <row r="35" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D35" s="45"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-    </row>
-    <row r="36" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D36" s="45"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-    </row>
-    <row r="37" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D37" s="44"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="43"/>
-    </row>
-    <row r="38" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D38" s="44"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="43"/>
-    </row>
-    <row r="39" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D39" s="44"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="K39" s="43"/>
-    </row>
-    <row r="40" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D40" s="45"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="43"/>
-    </row>
-    <row r="41" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D41" s="45"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-    </row>
-    <row r="42" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D42" s="45"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-    </row>
-    <row r="43" spans="3:11" x14ac:dyDescent="0.5">
-      <c r="D43" s="45"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="43"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="31"/>
+    </row>
+    <row r="27" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="71"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="31"/>
+    </row>
+    <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="71"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="31"/>
+    </row>
+    <row r="29" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="71"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="31"/>
+    </row>
+    <row r="30" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="71"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="31"/>
+    </row>
+    <row r="31" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="71"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="31"/>
+    </row>
+    <row r="32" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="71"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="31"/>
+    </row>
+    <row r="33" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A33" s="38"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="95"/>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="95"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="31"/>
+    </row>
+    <row r="34" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A34" s="65"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="50"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="26"/>
+    </row>
+    <row r="35" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="D35" s="12"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A36" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36" s="58"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="42"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A37" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="68"/>
+      <c r="C37" s="64"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A38" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="60"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
+      <c r="L38" s="40"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A39" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="58"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E40" s="42"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E41" s="42"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E42" s="42"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="40"/>
+      <c r="K42" s="40"/>
+      <c r="L42" s="40"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E43" s="41"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="40"/>
+      <c r="L43" s="40"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E44" s="41"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="40"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="40"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E45" s="41"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E46" s="42"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="40"/>
+      <c r="K46" s="40"/>
+      <c r="L46" s="40"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E47" s="42"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="E48" s="42"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="40"/>
+    </row>
+    <row r="49" spans="5:11" x14ac:dyDescent="0.5">
+      <c r="E49" s="42"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A6:C8"/>
-    <mergeCell ref="A9:C11"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
+  <mergeCells count="33">
+    <mergeCell ref="C33:K33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A6:D8"/>
+    <mergeCell ref="A9:D11"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:J27"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/docs/templates/A0-SHORE.xlsx
+++ b/docs/templates/A0-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9072C8D0-2260-4CBE-B93C-3A3BCF6C5424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{098191F4-449D-462B-9E32-5DBFBA18574C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CF2CF30-9561-47AD-9AE4-D232BAF72AF9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{68DFBB0C-44C9-417A-8D07-87DE2F5554DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -519,79 +519,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="63"/>
       </left>
@@ -604,6 +531,79 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -751,7 +751,7 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="24" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -780,11 +780,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -796,95 +874,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{B2D45115-5A21-4C07-A199-BDC0ADEB367C}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{E07599C1-EE65-4008-A0E6-A70FF8503192}"/>
-    <cellStyle name="Normal_CHORE" xfId="4" xr:uid="{86101A8C-CAEE-47EC-B21F-4AB23C311EE4}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{6EB5AEDC-BD9D-421B-8B2B-A645F702CD3B}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{349C5D86-F5AC-4D88-8595-92C763ED4846}"/>
+    <cellStyle name="Normal_CHORE" xfId="4" xr:uid="{68B2BCB6-D049-47AE-BC30-3A769E35456D}"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="ปกติ 10" xfId="6" xr:uid="{4503FE9E-942A-402A-B1F9-059A2AA8D545}"/>
+    <cellStyle name="ปกติ 10" xfId="6" xr:uid="{862FD919-CA09-433D-9909-8B46B00BCF01}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -916,10 +916,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10268" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
+        <xdr:cNvPr id="10270" name="Picture 5" descr="BV_3Certification_Numer_for LCB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7647A17-E2FE-C195-FA21-9FC77ACEB77C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90AC7B45-5698-5736-F2B0-81535F4AACF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -990,10 +990,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10269" name="Picture 23" descr="Logos">
+        <xdr:cNvPr id="10271" name="Picture 23" descr="Logos">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF952D7E-8DCB-2514-5E12-E2F713D99735}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E680414A-3B0E-27E6-3361-7C68CA2B8F12}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1016,7 +1016,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6263640" y="38100"/>
+          <a:off x="6697980" y="38100"/>
           <a:ext cx="1219200" cy="411480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1401,7 +1401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA3B5D7D-F151-410D-8E56-3925B9E5AB6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83D60A4E-C646-4079-98CD-B31440BAB435}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1411,8 +1411,8 @@
     <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="2.88671875" style="1" customWidth="1"/>
     <col min="3" max="3" width="4.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="6.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.88671875" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" style="1" customWidth="1"/>
@@ -1424,52 +1424,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3" spans="1:12" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="88"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="87"/>
     </row>
     <row r="4" spans="1:12" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="91"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="90"/>
     </row>
     <row r="5" spans="1:12" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A5" s="3" t="s">
@@ -1488,30 +1488,30 @@
       <c r="L5" s="15"/>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="76"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="75"/>
       <c r="E6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
       <c r="I6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
       <c r="L6" s="16"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A7" s="77"/>
-      <c r="B7" s="78"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="79"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="78"/>
       <c r="E7" s="18" t="s">
         <v>21</v>
       </c>
@@ -1524,10 +1524,10 @@
       <c r="L7" s="5"/>
     </row>
     <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="80"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="82"/>
+      <c r="A8" s="79"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="81"/>
       <c r="E8" s="7" t="s">
         <v>17</v>
       </c>
@@ -1546,22 +1546,22 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="85"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="84"/>
       <c r="E9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L9" s="19"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A10" s="83"/>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="85"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="84"/>
       <c r="E10" s="18" t="s">
         <v>20</v>
       </c>
@@ -1574,10 +1574,10 @@
       <c r="L10" s="5"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A11" s="83"/>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="85"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="84"/>
       <c r="E11" s="7" t="s">
         <v>17</v>
       </c>
@@ -1612,14 +1612,14 @@
       <c r="L12" s="23"/>
     </row>
     <row r="13" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="92" t="s">
+      <c r="A13" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="92"/>
-      <c r="C13" s="69" t="s">
+      <c r="B13" s="91"/>
+      <c r="C13" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="70"/>
+      <c r="D13" s="96"/>
       <c r="E13" s="24" t="s">
         <v>5</v>
       </c>
@@ -1646,10 +1646,10 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
       <c r="E14" s="43"/>
       <c r="F14" s="44"/>
       <c r="G14" s="45"/>
@@ -1662,8 +1662,8 @@
     <row r="15" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="38"/>
       <c r="B15" s="39"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="69"/>
       <c r="E15" s="43"/>
       <c r="F15" s="44"/>
       <c r="G15" s="45"/>
@@ -1676,8 +1676,8 @@
     <row r="16" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="38"/>
       <c r="B16" s="39"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="69"/>
       <c r="E16" s="43"/>
       <c r="F16" s="44"/>
       <c r="G16" s="45"/>
@@ -1690,8 +1690,8 @@
     <row r="17" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="38"/>
       <c r="B17" s="39"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="69"/>
       <c r="E17" s="43"/>
       <c r="F17" s="44"/>
       <c r="G17" s="45"/>
@@ -1704,8 +1704,8 @@
     <row r="18" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="38"/>
       <c r="B18" s="39"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="39"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="69"/>
       <c r="E18" s="43"/>
       <c r="F18" s="44"/>
       <c r="G18" s="45"/>
@@ -1718,8 +1718,8 @@
     <row r="19" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="38"/>
       <c r="B19" s="39"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="39"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="69"/>
       <c r="E19" s="43"/>
       <c r="F19" s="44"/>
       <c r="G19" s="45"/>
@@ -1732,8 +1732,8 @@
     <row r="20" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="38"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="39"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="69"/>
       <c r="E20" s="43"/>
       <c r="F20" s="44"/>
       <c r="G20" s="45"/>
@@ -1746,8 +1746,8 @@
     <row r="21" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="38"/>
       <c r="B21" s="39"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="39"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="69"/>
       <c r="E21" s="43"/>
       <c r="F21" s="44"/>
       <c r="G21" s="45"/>
@@ -1760,8 +1760,8 @@
     <row r="22" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="38"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="39"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="69"/>
       <c r="E22" s="43"/>
       <c r="F22" s="44"/>
       <c r="G22" s="45"/>
@@ -1774,8 +1774,8 @@
     <row r="23" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="38"/>
       <c r="B23" s="39"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="39"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="69"/>
       <c r="E23" s="43"/>
       <c r="F23" s="44"/>
       <c r="G23" s="45"/>
@@ -1786,10 +1786,10 @@
       <c r="L23" s="43"/>
     </row>
     <row r="24" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="71"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="72"/>
+      <c r="A24" s="68"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="69"/>
       <c r="E24" s="43"/>
       <c r="F24" s="44"/>
       <c r="G24" s="45"/>
@@ -1800,10 +1800,10 @@
       <c r="L24" s="43"/>
     </row>
     <row r="25" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="71"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="72"/>
+      <c r="A25" s="68"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
       <c r="E25" s="31"/>
       <c r="F25" s="32"/>
       <c r="G25" s="33"/>
@@ -1814,10 +1814,10 @@
       <c r="L25" s="31"/>
     </row>
     <row r="26" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="71"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
+      <c r="A26" s="68"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
       <c r="E26" s="31"/>
       <c r="F26" s="32"/>
       <c r="G26" s="33"/>
@@ -1828,10 +1828,10 @@
       <c r="L26" s="31"/>
     </row>
     <row r="27" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="71"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="72"/>
+      <c r="A27" s="68"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="69"/>
       <c r="E27" s="31"/>
       <c r="F27" s="32"/>
       <c r="G27" s="33"/>
@@ -1842,10 +1842,10 @@
       <c r="L27" s="31"/>
     </row>
     <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="71"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="72"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="69"/>
       <c r="E28" s="31"/>
       <c r="F28" s="32"/>
       <c r="G28" s="33"/>
@@ -1856,10 +1856,10 @@
       <c r="L28" s="31"/>
     </row>
     <row r="29" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="71"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="72"/>
+      <c r="A29" s="68"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="69"/>
       <c r="E29" s="31"/>
       <c r="F29" s="32"/>
       <c r="G29" s="33"/>
@@ -1870,10 +1870,10 @@
       <c r="L29" s="31"/>
     </row>
     <row r="30" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="71"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="72"/>
+      <c r="A30" s="68"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="69"/>
       <c r="E30" s="31"/>
       <c r="F30" s="32"/>
       <c r="G30" s="33"/>
@@ -1884,10 +1884,10 @@
       <c r="L30" s="31"/>
     </row>
     <row r="31" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="71"/>
-      <c r="B31" s="72"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="72"/>
+      <c r="A31" s="68"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="69"/>
       <c r="E31" s="31"/>
       <c r="F31" s="32"/>
       <c r="G31" s="33"/>
@@ -1898,10 +1898,10 @@
       <c r="L31" s="31"/>
     </row>
     <row r="32" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="72"/>
+      <c r="A32" s="68"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="69"/>
       <c r="E32" s="31"/>
       <c r="F32" s="32"/>
       <c r="G32" s="33"/>
@@ -1914,24 +1914,24 @@
     <row r="33" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="38"/>
       <c r="B33" s="39"/>
-      <c r="C33" s="94" t="s">
+      <c r="C33" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="95"/>
-      <c r="E33" s="95"/>
-      <c r="F33" s="95"/>
-      <c r="G33" s="95"/>
-      <c r="H33" s="95"/>
-      <c r="I33" s="95"/>
-      <c r="J33" s="95"/>
-      <c r="K33" s="96"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="67"/>
       <c r="L33" s="31"/>
     </row>
     <row r="34" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="65"/>
-      <c r="B34" s="66"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="66"/>
+      <c r="A34" s="70"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="71"/>
       <c r="E34" s="49" t="s">
         <v>27</v>
       </c>
@@ -1971,10 +1971,10 @@
       <c r="L36" s="42"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A37" s="67" t="s">
+      <c r="A37" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="68"/>
+      <c r="B37" s="94"/>
       <c r="C37" s="64"/>
       <c r="E37" s="58"/>
       <c r="F37" s="58"/>
@@ -2116,14 +2116,23 @@
       <c r="K49" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="C33:K33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
+  <mergeCells count="42">
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="A2:L2"/>
@@ -2134,22 +2143,22 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C33:K33"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
